--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4159"/>
+  <dimension ref="A1:F4160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83604,7 +83604,27 @@
         <v>105.6600036621094</v>
       </c>
       <c r="F4159" t="n">
-        <v>1241056</v>
+        <v>1241218</v>
+      </c>
+    </row>
+    <row r="4160">
+      <c r="A4160" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4160" t="n">
+        <v>107.73</v>
+      </c>
+      <c r="C4160" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="D4160" t="n">
+        <v>107.71</v>
+      </c>
+      <c r="E4160" t="n">
+        <v>108.31</v>
+      </c>
+      <c r="F4160" t="n">
+        <v>251363</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -83612,19 +83612,19 @@
         <v>46231</v>
       </c>
       <c r="B4160" t="n">
-        <v>107.73</v>
+        <v>107.98</v>
       </c>
       <c r="C4160" t="n">
         <v>109.62</v>
       </c>
       <c r="D4160" t="n">
-        <v>107.71</v>
+        <v>107.62</v>
       </c>
       <c r="E4160" t="n">
         <v>108.31</v>
       </c>
       <c r="F4160" t="n">
-        <v>251363</v>
+        <v>713023</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -83612,19 +83612,19 @@
         <v>46231</v>
       </c>
       <c r="B4160" t="n">
-        <v>107.98</v>
+        <v>107.17</v>
       </c>
       <c r="C4160" t="n">
         <v>109.62</v>
       </c>
       <c r="D4160" t="n">
-        <v>107.62</v>
+        <v>107.12</v>
       </c>
       <c r="E4160" t="n">
         <v>108.31</v>
       </c>
       <c r="F4160" t="n">
-        <v>713023</v>
+        <v>1155495</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -83612,16 +83612,16 @@
         <v>46231</v>
       </c>
       <c r="B4160" t="n">
-        <v>107.17</v>
+        <v>107.1699981689453</v>
       </c>
       <c r="C4160" t="n">
-        <v>109.62</v>
+        <v>109.620002746582</v>
       </c>
       <c r="D4160" t="n">
-        <v>107.12</v>
+        <v>107.120002746582</v>
       </c>
       <c r="E4160" t="n">
-        <v>108.31</v>
+        <v>108.3099975585938</v>
       </c>
       <c r="F4160" t="n">
         <v>1155495</v>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4160"/>
+  <dimension ref="A1:F4161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83627,6 +83627,26 @@
         <v>1155495</v>
       </c>
     </row>
+    <row r="4161">
+      <c r="A4161" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4161" t="n">
+        <v>105.42</v>
+      </c>
+      <c r="C4161" t="n">
+        <v>107.41</v>
+      </c>
+      <c r="D4161" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="E4161" t="n">
+        <v>107.11</v>
+      </c>
+      <c r="F4161" t="n">
+        <v>576559</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -83632,19 +83632,19 @@
         <v>46232</v>
       </c>
       <c r="B4161" t="n">
-        <v>105.42</v>
+        <v>105.1</v>
       </c>
       <c r="C4161" t="n">
         <v>107.41</v>
       </c>
       <c r="D4161" t="n">
-        <v>105.15</v>
+        <v>105.1</v>
       </c>
       <c r="E4161" t="n">
         <v>107.11</v>
       </c>
       <c r="F4161" t="n">
-        <v>576559</v>
+        <v>1094534</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4161"/>
+  <dimension ref="A1:F4162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83632,19 +83632,39 @@
         <v>46232</v>
       </c>
       <c r="B4161" t="n">
-        <v>105.1</v>
+        <v>105.0999984741211</v>
       </c>
       <c r="C4161" t="n">
-        <v>107.41</v>
+        <v>107.4100036621094</v>
       </c>
       <c r="D4161" t="n">
-        <v>105.1</v>
+        <v>105.0999984741211</v>
       </c>
       <c r="E4161" t="n">
-        <v>107.11</v>
+        <v>107.1100006103516</v>
       </c>
       <c r="F4161" t="n">
         <v>1094534</v>
+      </c>
+    </row>
+    <row r="4162">
+      <c r="A4162" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4162" t="n">
+        <v>107.36</v>
+      </c>
+      <c r="C4162" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="D4162" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="E4162" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="F4162" t="n">
+        <v>1504042</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4162"/>
+  <dimension ref="A1:F4163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83652,19 +83652,39 @@
         <v>46233</v>
       </c>
       <c r="B4162" t="n">
-        <v>107.36</v>
+        <v>107.3600006103516</v>
       </c>
       <c r="C4162" t="n">
-        <v>110.1</v>
+        <v>110.0999984741211</v>
       </c>
       <c r="D4162" t="n">
-        <v>105.6</v>
+        <v>105.5999984741211</v>
       </c>
       <c r="E4162" t="n">
-        <v>105.9</v>
+        <v>105.9000015258789</v>
       </c>
       <c r="F4162" t="n">
         <v>1504042</v>
+      </c>
+    </row>
+    <row r="4163">
+      <c r="A4163" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4163" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="C4163" t="n">
+        <v>107.97</v>
+      </c>
+      <c r="D4163" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="E4163" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="F4163" t="n">
+        <v>375561</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4163"/>
+  <dimension ref="A1:F4164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83675,16 +83675,36 @@
         <v>107.25</v>
       </c>
       <c r="C4163" t="n">
-        <v>107.97</v>
+        <v>107.9700012207031</v>
       </c>
       <c r="D4163" t="n">
-        <v>107.15</v>
+        <v>107.1500015258789</v>
       </c>
       <c r="E4163" t="n">
-        <v>107.46</v>
+        <v>107.4599990844727</v>
       </c>
       <c r="F4163" t="n">
-        <v>375561</v>
+        <v>375711</v>
+      </c>
+    </row>
+    <row r="4164">
+      <c r="A4164" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4164" t="n">
+        <v>108.38</v>
+      </c>
+      <c r="C4164" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="D4164" t="n">
+        <v>107.32</v>
+      </c>
+      <c r="E4164" t="n">
+        <v>108</v>
+      </c>
+      <c r="F4164" t="n">
+        <v>1056800</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4164"/>
+  <dimension ref="A1:F4165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83692,19 +83692,39 @@
         <v>46237</v>
       </c>
       <c r="B4164" t="n">
-        <v>108.38</v>
+        <v>108.379997253418</v>
       </c>
       <c r="C4164" t="n">
-        <v>108.45</v>
+        <v>108.4499969482422</v>
       </c>
       <c r="D4164" t="n">
-        <v>107.32</v>
+        <v>107.2900009155273</v>
       </c>
       <c r="E4164" t="n">
         <v>108</v>
       </c>
       <c r="F4164" t="n">
         <v>1056800</v>
+      </c>
+    </row>
+    <row r="4165">
+      <c r="A4165" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B4165" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="C4165" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="D4165" t="n">
+        <v>107.67</v>
+      </c>
+      <c r="E4165" t="n">
+        <v>109.67</v>
+      </c>
+      <c r="F4165" t="n">
+        <v>1881696</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4165"/>
+  <dimension ref="A1:F4166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83712,19 +83712,39 @@
         <v>46238</v>
       </c>
       <c r="B4165" t="n">
-        <v>108.15</v>
+        <v>108.1500015258789</v>
       </c>
       <c r="C4165" t="n">
-        <v>110.2</v>
+        <v>110.1999969482422</v>
       </c>
       <c r="D4165" t="n">
-        <v>107.67</v>
+        <v>107.6699981689453</v>
       </c>
       <c r="E4165" t="n">
-        <v>109.67</v>
+        <v>109.6699981689453</v>
       </c>
       <c r="F4165" t="n">
         <v>1881696</v>
+      </c>
+    </row>
+    <row r="4166">
+      <c r="A4166" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4166" t="n">
+        <v>107.79</v>
+      </c>
+      <c r="C4166" t="n">
+        <v>109.78</v>
+      </c>
+      <c r="D4166" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="E4166" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="F4166" t="n">
+        <v>2270465</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4166"/>
+  <dimension ref="A1:F4167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83732,19 +83732,39 @@
         <v>46239</v>
       </c>
       <c r="B4166" t="n">
-        <v>107.79</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="C4166" t="n">
-        <v>109.78</v>
+        <v>109.7799987792969</v>
       </c>
       <c r="D4166" t="n">
-        <v>107.65</v>
+        <v>107.6500015258789</v>
       </c>
       <c r="E4166" t="n">
-        <v>108.35</v>
+        <v>108.3499984741211</v>
       </c>
       <c r="F4166" t="n">
         <v>2270465</v>
+      </c>
+    </row>
+    <row r="4167">
+      <c r="A4167" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4167" t="n">
+        <v>105.91</v>
+      </c>
+      <c r="C4167" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="D4167" t="n">
+        <v>105.61</v>
+      </c>
+      <c r="E4167" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F4167" t="n">
+        <v>1596408</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4167"/>
+  <dimension ref="A1:F4168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83752,19 +83752,39 @@
         <v>46240</v>
       </c>
       <c r="B4167" t="n">
-        <v>105.91</v>
+        <v>105.9100036621094</v>
       </c>
       <c r="C4167" t="n">
-        <v>107.55</v>
+        <v>107.5500030517578</v>
       </c>
       <c r="D4167" t="n">
-        <v>105.61</v>
+        <v>105.6100006103516</v>
       </c>
       <c r="E4167" t="n">
-        <v>107.4</v>
+        <v>107.4000015258789</v>
       </c>
       <c r="F4167" t="n">
         <v>1596408</v>
+      </c>
+    </row>
+    <row r="4168">
+      <c r="A4168" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4168" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="C4168" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="D4168" t="n">
+        <v>103.94</v>
+      </c>
+      <c r="E4168" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="F4168" t="n">
+        <v>1789496</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4168"/>
+  <dimension ref="A1:F4169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83772,19 +83772,39 @@
         <v>46241</v>
       </c>
       <c r="B4168" t="n">
-        <v>104.7</v>
+        <v>104.6999969482422</v>
       </c>
       <c r="C4168" t="n">
-        <v>106.1</v>
+        <v>106.0999984741211</v>
       </c>
       <c r="D4168" t="n">
-        <v>103.94</v>
+        <v>103.9400024414062</v>
       </c>
       <c r="E4168" t="n">
-        <v>105.88</v>
+        <v>105.879997253418</v>
       </c>
       <c r="F4168" t="n">
         <v>1789496</v>
+      </c>
+    </row>
+    <row r="4169">
+      <c r="A4169" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4169" t="n">
+        <v>103.52</v>
+      </c>
+      <c r="C4169" t="n">
+        <v>105.46</v>
+      </c>
+      <c r="D4169" t="n">
+        <v>103.52</v>
+      </c>
+      <c r="E4169" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="F4169" t="n">
+        <v>764939</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4169"/>
+  <dimension ref="A1:F4170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83792,19 +83792,39 @@
         <v>46244</v>
       </c>
       <c r="B4169" t="n">
-        <v>103.52</v>
+        <v>103.5199966430664</v>
       </c>
       <c r="C4169" t="n">
-        <v>105.46</v>
+        <v>105.4599990844727</v>
       </c>
       <c r="D4169" t="n">
-        <v>103.52</v>
+        <v>103.5199966430664</v>
       </c>
       <c r="E4169" t="n">
-        <v>104.47</v>
+        <v>104.4700012207031</v>
       </c>
       <c r="F4169" t="n">
         <v>764939</v>
+      </c>
+    </row>
+    <row r="4170">
+      <c r="A4170" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4170" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="C4170" t="n">
+        <v>104.19</v>
+      </c>
+      <c r="D4170" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="E4170" t="n">
+        <v>103.63</v>
+      </c>
+      <c r="F4170" t="n">
+        <v>2500078</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4170"/>
+  <dimension ref="A1:F4171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83812,19 +83812,39 @@
         <v>46245</v>
       </c>
       <c r="B4170" t="n">
-        <v>101.2</v>
+        <v>101.1999969482422</v>
       </c>
       <c r="C4170" t="n">
-        <v>104.19</v>
+        <v>104.1900024414062</v>
       </c>
       <c r="D4170" t="n">
-        <v>100.78</v>
+        <v>100.7799987792969</v>
       </c>
       <c r="E4170" t="n">
-        <v>103.63</v>
+        <v>103.629997253418</v>
       </c>
       <c r="F4170" t="n">
         <v>2500078</v>
+      </c>
+    </row>
+    <row r="4171">
+      <c r="A4171" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4171" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="C4171" t="n">
+        <v>101.58</v>
+      </c>
+      <c r="D4171" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="E4171" t="n">
+        <v>101.27</v>
+      </c>
+      <c r="F4171" t="n">
+        <v>2991745</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4171"/>
+  <dimension ref="A1:F4172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83832,19 +83832,39 @@
         <v>46246</v>
       </c>
       <c r="B4171" t="n">
-        <v>100.77</v>
+        <v>100.7699966430664</v>
       </c>
       <c r="C4171" t="n">
-        <v>101.58</v>
+        <v>101.5800018310547</v>
       </c>
       <c r="D4171" t="n">
-        <v>100.06</v>
+        <v>100.0599975585938</v>
       </c>
       <c r="E4171" t="n">
-        <v>101.27</v>
+        <v>101.2699966430664</v>
       </c>
       <c r="F4171" t="n">
         <v>2991745</v>
+      </c>
+    </row>
+    <row r="4172">
+      <c r="A4172" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4172" t="n">
+        <v>100.97</v>
+      </c>
+      <c r="C4172" t="n">
+        <v>102.11</v>
+      </c>
+      <c r="D4172" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="E4172" t="n">
+        <v>100.47</v>
+      </c>
+      <c r="F4172" t="n">
+        <v>1859969</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4172"/>
+  <dimension ref="A1:F4173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83851,20 +83851,32 @@
       <c r="A4172" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B4172" t="n">
-        <v>100.97</v>
-      </c>
-      <c r="C4172" t="n">
-        <v>102.11</v>
-      </c>
-      <c r="D4172" t="n">
-        <v>100.32</v>
-      </c>
-      <c r="E4172" t="n">
-        <v>100.47</v>
-      </c>
+      <c r="B4172" t="inlineStr"/>
+      <c r="C4172" t="inlineStr"/>
+      <c r="D4172" t="inlineStr"/>
+      <c r="E4172" t="inlineStr"/>
       <c r="F4172" t="n">
-        <v>1859969</v>
+        <v>2679855</v>
+      </c>
+    </row>
+    <row r="4173">
+      <c r="A4173" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4173" t="n">
+        <v>100.12</v>
+      </c>
+      <c r="C4173" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="D4173" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="E4173" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="F4173" t="n">
+        <v>2691974</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4173"/>
+  <dimension ref="A1:F4174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83851,12 +83851,20 @@
       <c r="A4172" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B4172" t="inlineStr"/>
-      <c r="C4172" t="inlineStr"/>
-      <c r="D4172" t="inlineStr"/>
-      <c r="E4172" t="inlineStr"/>
+      <c r="B4172" t="n">
+        <v>100.9700012207031</v>
+      </c>
+      <c r="C4172" t="n">
+        <v>102.1100006103516</v>
+      </c>
+      <c r="D4172" t="n">
+        <v>100.3199996948242</v>
+      </c>
+      <c r="E4172" t="n">
+        <v>100.4700012207031</v>
+      </c>
       <c r="F4172" t="n">
-        <v>2679855</v>
+        <v>1859969</v>
       </c>
     </row>
     <row r="4173">
@@ -83864,19 +83872,39 @@
         <v>46248</v>
       </c>
       <c r="B4173" t="n">
-        <v>100.12</v>
+        <v>100.120002746582</v>
       </c>
       <c r="C4173" t="n">
-        <v>100.51</v>
+        <v>100.5100021362305</v>
       </c>
       <c r="D4173" t="n">
-        <v>98.45999999999999</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="E4173" t="n">
-        <v>100.38</v>
+        <v>100.379997253418</v>
       </c>
       <c r="F4173" t="n">
         <v>2691974</v>
+      </c>
+    </row>
+    <row r="4174">
+      <c r="A4174" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4174" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4174" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="D4174" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="E4174" t="n">
+        <v>100.39</v>
+      </c>
+      <c r="F4174" t="n">
+        <v>941991</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4174"/>
+  <dimension ref="A1:F4175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83895,16 +83895,36 @@
         <v>100</v>
       </c>
       <c r="C4174" t="n">
-        <v>100.72</v>
+        <v>100.7200012207031</v>
       </c>
       <c r="D4174" t="n">
-        <v>99.65000000000001</v>
+        <v>99.65000152587891</v>
       </c>
       <c r="E4174" t="n">
-        <v>100.39</v>
+        <v>100.3899993896484</v>
       </c>
       <c r="F4174" t="n">
         <v>941991</v>
+      </c>
+    </row>
+    <row r="4175">
+      <c r="A4175" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B4175" t="n">
+        <v>99</v>
+      </c>
+      <c r="C4175" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="D4175" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="E4175" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="F4175" t="n">
+        <v>871961</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4175"/>
+  <dimension ref="A1:F4176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83915,16 +83915,36 @@
         <v>99</v>
       </c>
       <c r="C4175" t="n">
-        <v>100.7</v>
+        <v>100.6999969482422</v>
       </c>
       <c r="D4175" t="n">
-        <v>98.92</v>
+        <v>98.91999816894531</v>
       </c>
       <c r="E4175" t="n">
-        <v>99.8</v>
+        <v>99.80000305175781</v>
       </c>
       <c r="F4175" t="n">
         <v>871961</v>
+      </c>
+    </row>
+    <row r="4176">
+      <c r="A4176" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4176" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="C4176" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="D4176" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E4176" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="F4176" t="n">
+        <v>2176571</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4176"/>
+  <dimension ref="A1:F4177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83932,19 +83932,39 @@
         <v>46253</v>
       </c>
       <c r="B4176" t="n">
-        <v>99.94</v>
+        <v>99.94000244140625</v>
       </c>
       <c r="C4176" t="n">
-        <v>101.85</v>
+        <v>101.8499984741211</v>
       </c>
       <c r="D4176" t="n">
-        <v>99.40000000000001</v>
+        <v>99.40000152587891</v>
       </c>
       <c r="E4176" t="n">
-        <v>100.35</v>
+        <v>100.3499984741211</v>
       </c>
       <c r="F4176" t="n">
         <v>2176571</v>
+      </c>
+    </row>
+    <row r="4177">
+      <c r="A4177" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4177" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="C4177" t="n">
+        <v>100.64</v>
+      </c>
+      <c r="D4177" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="E4177" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="F4177" t="n">
+        <v>1694811</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4177"/>
+  <dimension ref="A1:F4178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83955,16 +83955,36 @@
         <v>99.25</v>
       </c>
       <c r="C4177" t="n">
-        <v>100.64</v>
+        <v>100.6399993896484</v>
       </c>
       <c r="D4177" t="n">
-        <v>98.95</v>
+        <v>98.94999694824219</v>
       </c>
       <c r="E4177" t="n">
-        <v>99.41</v>
+        <v>99.41000366210938</v>
       </c>
       <c r="F4177" t="n">
         <v>1694811</v>
+      </c>
+    </row>
+    <row r="4178">
+      <c r="A4178" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4178" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="C4178" t="n">
+        <v>102.49</v>
+      </c>
+      <c r="D4178" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="E4178" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="F4178" t="n">
+        <v>3646974</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4178"/>
+  <dimension ref="A1:F4179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83975,16 +83975,36 @@
         <v>102.25</v>
       </c>
       <c r="C4178" t="n">
-        <v>102.49</v>
+        <v>102.4899978637695</v>
       </c>
       <c r="D4178" t="n">
-        <v>99.66</v>
+        <v>99.66000366210938</v>
       </c>
       <c r="E4178" t="n">
         <v>100.25</v>
       </c>
       <c r="F4178" t="n">
-        <v>3646974</v>
+        <v>3646368</v>
+      </c>
+    </row>
+    <row r="4179">
+      <c r="A4179" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4179" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="C4179" t="n">
+        <v>103.69</v>
+      </c>
+      <c r="D4179" t="n">
+        <v>101</v>
+      </c>
+      <c r="E4179" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="F4179" t="n">
+        <v>906955</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4179"/>
+  <dimension ref="A1:F4180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83991,20 +83991,32 @@
       <c r="A4179" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B4179" t="n">
-        <v>102.64</v>
-      </c>
-      <c r="C4179" t="n">
-        <v>103.69</v>
-      </c>
-      <c r="D4179" t="n">
-        <v>101</v>
-      </c>
-      <c r="E4179" t="n">
-        <v>101.5</v>
-      </c>
+      <c r="B4179" t="inlineStr"/>
+      <c r="C4179" t="inlineStr"/>
+      <c r="D4179" t="inlineStr"/>
+      <c r="E4179" t="inlineStr"/>
       <c r="F4179" t="n">
-        <v>906955</v>
+        <v>1414032</v>
+      </c>
+    </row>
+    <row r="4180">
+      <c r="A4180" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4180" t="n">
+        <v>105.24</v>
+      </c>
+      <c r="C4180" t="n">
+        <v>105.38</v>
+      </c>
+      <c r="D4180" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="E4180" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="F4180" t="n">
+        <v>1414158</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4180"/>
+  <dimension ref="A1:F4181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83991,12 +83991,20 @@
       <c r="A4179" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B4179" t="inlineStr"/>
-      <c r="C4179" t="inlineStr"/>
-      <c r="D4179" t="inlineStr"/>
-      <c r="E4179" t="inlineStr"/>
+      <c r="B4179" t="n">
+        <v>102.6399993896484</v>
+      </c>
+      <c r="C4179" t="n">
+        <v>103.6900024414062</v>
+      </c>
+      <c r="D4179" t="n">
+        <v>101</v>
+      </c>
+      <c r="E4179" t="n">
+        <v>101.5</v>
+      </c>
       <c r="F4179" t="n">
-        <v>1414032</v>
+        <v>906955</v>
       </c>
     </row>
     <row r="4180">
@@ -84004,19 +84012,39 @@
         <v>46259</v>
       </c>
       <c r="B4180" t="n">
-        <v>105.24</v>
+        <v>105.2399978637695</v>
       </c>
       <c r="C4180" t="n">
-        <v>105.38</v>
+        <v>105.379997253418</v>
       </c>
       <c r="D4180" t="n">
-        <v>102.28</v>
+        <v>102.2799987792969</v>
       </c>
       <c r="E4180" t="n">
         <v>102.5</v>
       </c>
       <c r="F4180" t="n">
         <v>1414158</v>
+      </c>
+    </row>
+    <row r="4181">
+      <c r="A4181" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4181" t="n">
+        <v>104.8000030517578</v>
+      </c>
+      <c r="C4181" t="n">
+        <v>106.3399963378906</v>
+      </c>
+      <c r="D4181" t="n">
+        <v>104.5500030517578</v>
+      </c>
+      <c r="E4181" t="n">
+        <v>105.1500015258789</v>
+      </c>
+      <c r="F4181" t="n">
+        <v>1851770</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4181"/>
+  <dimension ref="A1:F4182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83984,7 +83984,7 @@
         <v>100.25</v>
       </c>
       <c r="F4178" t="n">
-        <v>3646368</v>
+        <v>3646974</v>
       </c>
     </row>
     <row r="4179">
@@ -84044,7 +84044,27 @@
         <v>105.1500015258789</v>
       </c>
       <c r="F4181" t="n">
-        <v>1851770</v>
+        <v>1851827</v>
+      </c>
+    </row>
+    <row r="4182">
+      <c r="A4182" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4182" t="n">
+        <v>105.17</v>
+      </c>
+      <c r="C4182" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="D4182" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="E4182" t="n">
+        <v>104.53</v>
+      </c>
+      <c r="F4182" t="n">
+        <v>2053956</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4182"/>
+  <dimension ref="A1:F4183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83984,7 +83984,7 @@
         <v>100.25</v>
       </c>
       <c r="F4178" t="n">
-        <v>3646974</v>
+        <v>3646368</v>
       </c>
     </row>
     <row r="4179">
@@ -84051,20 +84051,32 @@
       <c r="A4182" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B4182" t="n">
-        <v>105.17</v>
-      </c>
-      <c r="C4182" t="n">
-        <v>105.8</v>
-      </c>
-      <c r="D4182" t="n">
-        <v>104.43</v>
-      </c>
-      <c r="E4182" t="n">
-        <v>104.53</v>
-      </c>
+      <c r="B4182" t="inlineStr"/>
+      <c r="C4182" t="inlineStr"/>
+      <c r="D4182" t="inlineStr"/>
+      <c r="E4182" t="inlineStr"/>
       <c r="F4182" t="n">
-        <v>2053956</v>
+        <v>1125093</v>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B4183" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="C4183" t="n">
+        <v>105.99</v>
+      </c>
+      <c r="D4183" t="n">
+        <v>103.21</v>
+      </c>
+      <c r="E4183" t="n">
+        <v>105.52</v>
+      </c>
+      <c r="F4183" t="n">
+        <v>1125039</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -84056,7 +84056,7 @@
       <c r="D4182" t="inlineStr"/>
       <c r="E4182" t="inlineStr"/>
       <c r="F4182" t="n">
-        <v>1125093</v>
+        <v>2154613</v>
       </c>
     </row>
     <row r="4183">
@@ -84064,7 +84064,7 @@
         <v>46262</v>
       </c>
       <c r="B4183" t="n">
-        <v>104.1</v>
+        <v>104.58</v>
       </c>
       <c r="C4183" t="n">
         <v>105.99</v>
@@ -84076,7 +84076,7 @@
         <v>105.52</v>
       </c>
       <c r="F4183" t="n">
-        <v>1125039</v>
+        <v>2154613</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4183"/>
+  <dimension ref="A1:F4182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84049,7 +84049,7 @@
     </row>
     <row r="4182">
       <c r="A4182" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B4182" t="inlineStr"/>
       <c r="C4182" t="inlineStr"/>
@@ -84059,26 +84059,6 @@
         <v>2154613</v>
       </c>
     </row>
-    <row r="4183">
-      <c r="A4183" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B4183" t="n">
-        <v>104.58</v>
-      </c>
-      <c r="C4183" t="n">
-        <v>105.99</v>
-      </c>
-      <c r="D4183" t="n">
-        <v>103.21</v>
-      </c>
-      <c r="E4183" t="n">
-        <v>105.52</v>
-      </c>
-      <c r="F4183" t="n">
-        <v>2154613</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4182"/>
+  <dimension ref="A1:F4185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83984,7 +83984,7 @@
         <v>100.25</v>
       </c>
       <c r="F4178" t="n">
-        <v>3646368</v>
+        <v>3646974</v>
       </c>
     </row>
     <row r="4179">
@@ -84049,14 +84049,82 @@
     </row>
     <row r="4182">
       <c r="A4182" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4182" t="n">
+        <v>105.1699981689453</v>
+      </c>
+      <c r="C4182" t="n">
+        <v>105.7900009155273</v>
+      </c>
+      <c r="D4182" t="n">
+        <v>104.4300003051758</v>
+      </c>
+      <c r="E4182" t="n">
+        <v>104.5299987792969</v>
+      </c>
+      <c r="F4182" t="n">
+        <v>2053956</v>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B4182" t="inlineStr"/>
-      <c r="C4182" t="inlineStr"/>
-      <c r="D4182" t="inlineStr"/>
-      <c r="E4182" t="inlineStr"/>
-      <c r="F4182" t="n">
-        <v>2154613</v>
+      <c r="B4183" t="n">
+        <v>104.5800018310547</v>
+      </c>
+      <c r="C4183" t="n">
+        <v>105.9899978637695</v>
+      </c>
+      <c r="D4183" t="n">
+        <v>103.2099990844727</v>
+      </c>
+      <c r="E4183" t="n">
+        <v>105.5199966430664</v>
+      </c>
+      <c r="F4183" t="n">
+        <v>2155615</v>
+      </c>
+    </row>
+    <row r="4184">
+      <c r="A4184" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B4184" t="n">
+        <v>106.129997253418</v>
+      </c>
+      <c r="C4184" t="n">
+        <v>106.7799987792969</v>
+      </c>
+      <c r="D4184" t="n">
+        <v>105.5100021362305</v>
+      </c>
+      <c r="E4184" t="n">
+        <v>105.8600006103516</v>
+      </c>
+      <c r="F4184" t="n">
+        <v>1788297</v>
+      </c>
+    </row>
+    <row r="4185">
+      <c r="A4185" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4185" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="C4185" t="n">
+        <v>108.54</v>
+      </c>
+      <c r="D4185" t="n">
+        <v>106</v>
+      </c>
+      <c r="E4185" t="n">
+        <v>106.86</v>
+      </c>
+      <c r="F4185" t="n">
+        <v>1374582</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4185"/>
+  <dimension ref="A1:F4186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84111,20 +84111,32 @@
       <c r="A4185" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B4185" t="n">
-        <v>107.7</v>
-      </c>
-      <c r="C4185" t="n">
-        <v>108.54</v>
-      </c>
-      <c r="D4185" t="n">
-        <v>106</v>
-      </c>
-      <c r="E4185" t="n">
-        <v>106.86</v>
-      </c>
+      <c r="B4185" t="inlineStr"/>
+      <c r="C4185" t="inlineStr"/>
+      <c r="D4185" t="inlineStr"/>
+      <c r="E4185" t="inlineStr"/>
       <c r="F4185" t="n">
-        <v>1374582</v>
+        <v>3821241</v>
+      </c>
+    </row>
+    <row r="4186">
+      <c r="A4186" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4186" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="C4186" t="n">
+        <v>111.88</v>
+      </c>
+      <c r="D4186" t="n">
+        <v>107.18</v>
+      </c>
+      <c r="E4186" t="n">
+        <v>108</v>
+      </c>
+      <c r="F4186" t="n">
+        <v>3821980</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4186"/>
+  <dimension ref="A1:F4187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84111,12 +84111,20 @@
       <c r="A4185" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B4185" t="inlineStr"/>
-      <c r="C4185" t="inlineStr"/>
-      <c r="D4185" t="inlineStr"/>
-      <c r="E4185" t="inlineStr"/>
+      <c r="B4185" t="n">
+        <v>107.6999969482422</v>
+      </c>
+      <c r="C4185" t="n">
+        <v>108.5400009155273</v>
+      </c>
+      <c r="D4185" t="n">
+        <v>106</v>
+      </c>
+      <c r="E4185" t="n">
+        <v>106.8600006103516</v>
+      </c>
       <c r="F4185" t="n">
-        <v>3821241</v>
+        <v>1374582</v>
       </c>
     </row>
     <row r="4186">
@@ -84124,19 +84132,39 @@
         <v>46267</v>
       </c>
       <c r="B4186" t="n">
-        <v>110.9</v>
+        <v>110.9000015258789</v>
       </c>
       <c r="C4186" t="n">
-        <v>111.88</v>
+        <v>111.8399963378906</v>
       </c>
       <c r="D4186" t="n">
-        <v>107.18</v>
+        <v>107.1800003051758</v>
       </c>
       <c r="E4186" t="n">
         <v>108</v>
       </c>
       <c r="F4186" t="n">
         <v>3821980</v>
+      </c>
+    </row>
+    <row r="4187">
+      <c r="A4187" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4187" t="n">
+        <v>111.06</v>
+      </c>
+      <c r="C4187" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="D4187" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="E4187" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="F4187" t="n">
+        <v>3123550</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4187"/>
+  <dimension ref="A1:F4188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84151,20 +84151,32 @@
       <c r="A4187" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B4187" t="n">
-        <v>111.06</v>
-      </c>
-      <c r="C4187" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="D4187" t="n">
-        <v>110.93</v>
-      </c>
-      <c r="E4187" t="n">
-        <v>112.5</v>
-      </c>
+      <c r="B4187" t="inlineStr"/>
+      <c r="C4187" t="inlineStr"/>
+      <c r="D4187" t="inlineStr"/>
+      <c r="E4187" t="inlineStr"/>
       <c r="F4187" t="n">
-        <v>3123550</v>
+        <v>1401572</v>
+      </c>
+    </row>
+    <row r="4188">
+      <c r="A4188" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4188" t="n">
+        <v>110.99</v>
+      </c>
+      <c r="C4188" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="D4188" t="n">
+        <v>109.76</v>
+      </c>
+      <c r="E4188" t="n">
+        <v>110</v>
+      </c>
+      <c r="F4188" t="n">
+        <v>1401579</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -84151,12 +84151,20 @@
       <c r="A4187" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B4187" t="inlineStr"/>
-      <c r="C4187" t="inlineStr"/>
-      <c r="D4187" t="inlineStr"/>
-      <c r="E4187" t="inlineStr"/>
+      <c r="B4187" t="n">
+        <v>111.0599975585938</v>
+      </c>
+      <c r="C4187" t="n">
+        <v>113.1999969482422</v>
+      </c>
+      <c r="D4187" t="n">
+        <v>110.9300003051758</v>
+      </c>
+      <c r="E4187" t="n">
+        <v>112.5</v>
+      </c>
       <c r="F4187" t="n">
-        <v>1401572</v>
+        <v>3123550</v>
       </c>
     </row>
     <row r="4188">
@@ -84164,13 +84172,13 @@
         <v>46269</v>
       </c>
       <c r="B4188" t="n">
-        <v>110.99</v>
+        <v>110.9899978637695</v>
       </c>
       <c r="C4188" t="n">
-        <v>112.05</v>
+        <v>112.0500030517578</v>
       </c>
       <c r="D4188" t="n">
-        <v>109.76</v>
+        <v>109.7600021362305</v>
       </c>
       <c r="E4188" t="n">
         <v>110</v>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4188"/>
+  <dimension ref="A1:F4189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84187,6 +84187,26 @@
         <v>1401579</v>
       </c>
     </row>
+    <row r="4189">
+      <c r="A4189" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4189" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="C4189" t="n">
+        <v>113.66</v>
+      </c>
+      <c r="D4189" t="n">
+        <v>111.69</v>
+      </c>
+      <c r="E4189" t="n">
+        <v>112.26</v>
+      </c>
+      <c r="F4189" t="n">
+        <v>2088675</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4189"/>
+  <dimension ref="A1:F4190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84207,6 +84207,26 @@
         <v>2088675</v>
       </c>
     </row>
+    <row r="4190">
+      <c r="A4190" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4190" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="C4190" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="D4190" t="n">
+        <v>109.71</v>
+      </c>
+      <c r="E4190" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F4190" t="n">
+        <v>1723035</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4190"/>
+  <dimension ref="A1:F4191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84192,16 +84192,16 @@
         <v>46273</v>
       </c>
       <c r="B4189" t="n">
-        <v>111.7</v>
+        <v>111.6999969482422</v>
       </c>
       <c r="C4189" t="n">
-        <v>113.66</v>
+        <v>113.6600036621094</v>
       </c>
       <c r="D4189" t="n">
-        <v>111.69</v>
+        <v>111.6900024414062</v>
       </c>
       <c r="E4189" t="n">
-        <v>112.26</v>
+        <v>112.2600021362305</v>
       </c>
       <c r="F4189" t="n">
         <v>2088675</v>
@@ -84212,19 +84212,39 @@
         <v>46274</v>
       </c>
       <c r="B4190" t="n">
-        <v>110.2</v>
+        <v>110.1999969482422</v>
       </c>
       <c r="C4190" t="n">
         <v>111.5</v>
       </c>
       <c r="D4190" t="n">
-        <v>109.71</v>
+        <v>109.7099990844727</v>
       </c>
       <c r="E4190" t="n">
         <v>111.5</v>
       </c>
       <c r="F4190" t="n">
         <v>1723035</v>
+      </c>
+    </row>
+    <row r="4191">
+      <c r="A4191" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4191" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="C4191" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="D4191" t="n">
+        <v>109.13</v>
+      </c>
+      <c r="E4191" t="n">
+        <v>109.54</v>
+      </c>
+      <c r="F4191" t="n">
+        <v>2641041</v>
       </c>
     </row>
   </sheetData>

--- a/database/SMAL11.xlsx
+++ b/database/SMAL11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4191"/>
+  <dimension ref="A1:F4192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84232,19 +84232,39 @@
         <v>46275</v>
       </c>
       <c r="B4191" t="n">
-        <v>112.3</v>
+        <v>112.3000030517578</v>
       </c>
       <c r="C4191" t="n">
-        <v>112.47</v>
+        <v>112.4700012207031</v>
       </c>
       <c r="D4191" t="n">
-        <v>109.13</v>
+        <v>109.129997253418</v>
       </c>
       <c r="E4191" t="n">
-        <v>109.54</v>
+        <v>109.5400009155273</v>
       </c>
       <c r="F4191" t="n">
         <v>2641041</v>
+      </c>
+    </row>
+    <row r="4192">
+      <c r="A4192" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4192" t="n">
+        <v>110.83</v>
+      </c>
+      <c r="C4192" t="n">
+        <v>112.74</v>
+      </c>
+      <c r="D4192" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E4192" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="F4192" t="n">
+        <v>3470198</v>
       </c>
     </row>
   </sheetData>
